--- a/summary_stats/chuuchuu_summary_2025_03.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_03.xlsx
@@ -1454,25 +1454,25 @@
         <v>87</v>
       </c>
       <c r="N13" t="n">
-        <v>987</v>
+        <v>951</v>
       </c>
       <c r="O13" t="n">
-        <v>818</v>
+        <v>783</v>
       </c>
       <c r="P13" t="n">
-        <v>761</v>
+        <v>727</v>
       </c>
       <c r="Q13" t="n">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="R13" t="n">
-        <v>460</v>
+        <v>437</v>
       </c>
       <c r="S13" t="n">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="T13" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
         <v>1830</v>
@@ -1612,25 +1612,25 @@
         <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="O15" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="P15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q15" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="R15" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="S15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U15" t="n">
         <v>362</v>
@@ -1691,25 +1691,25 @@
         <v>481</v>
       </c>
       <c r="N16" t="n">
-        <v>2181</v>
+        <v>2011</v>
       </c>
       <c r="O16" t="n">
-        <v>1790</v>
+        <v>1627</v>
       </c>
       <c r="P16" t="n">
-        <v>1624</v>
+        <v>1466</v>
       </c>
       <c r="Q16" t="n">
-        <v>1194</v>
+        <v>1059</v>
       </c>
       <c r="R16" t="n">
-        <v>861</v>
+        <v>743</v>
       </c>
       <c r="S16" t="n">
-        <v>348</v>
+        <v>282</v>
       </c>
       <c r="T16" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="U16" t="n">
         <v>3971</v>
@@ -1770,25 +1770,25 @@
         <v>122</v>
       </c>
       <c r="N17" t="n">
-        <v>805</v>
+        <v>768</v>
       </c>
       <c r="O17" t="n">
-        <v>648</v>
+        <v>613</v>
       </c>
       <c r="P17" t="n">
-        <v>600</v>
+        <v>565</v>
       </c>
       <c r="Q17" t="n">
-        <v>457</v>
+        <v>424</v>
       </c>
       <c r="R17" t="n">
-        <v>341</v>
+        <v>309</v>
       </c>
       <c r="S17" t="n">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="T17" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="U17" t="n">
         <v>1999</v>
@@ -1849,25 +1849,25 @@
         <v>1985</v>
       </c>
       <c r="N18" t="n">
-        <v>8244</v>
+        <v>7656</v>
       </c>
       <c r="O18" t="n">
-        <v>7089</v>
+        <v>6527</v>
       </c>
       <c r="P18" t="n">
-        <v>6599</v>
+        <v>6048</v>
       </c>
       <c r="Q18" t="n">
-        <v>5086</v>
+        <v>4607</v>
       </c>
       <c r="R18" t="n">
-        <v>3875</v>
+        <v>3438</v>
       </c>
       <c r="S18" t="n">
-        <v>1813</v>
+        <v>1505</v>
       </c>
       <c r="T18" t="n">
-        <v>482</v>
+        <v>348</v>
       </c>
       <c r="U18" t="n">
         <v>14134</v>
@@ -1928,25 +1928,25 @@
         <v>300</v>
       </c>
       <c r="N19" t="n">
-        <v>2025</v>
+        <v>1905</v>
       </c>
       <c r="O19" t="n">
-        <v>1642</v>
+        <v>1530</v>
       </c>
       <c r="P19" t="n">
-        <v>1539</v>
+        <v>1429</v>
       </c>
       <c r="Q19" t="n">
-        <v>1149</v>
+        <v>1052</v>
       </c>
       <c r="R19" t="n">
-        <v>890</v>
+        <v>802</v>
       </c>
       <c r="S19" t="n">
-        <v>431</v>
+        <v>368</v>
       </c>
       <c r="T19" t="n">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="U19" t="n">
         <v>3340</v>
@@ -2165,7 +2165,7 @@
         <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
@@ -2244,25 +2244,25 @@
         <v>69</v>
       </c>
       <c r="N23" t="n">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="O23" t="n">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="P23" t="n">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="Q23" t="n">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="R23" t="n">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="S23" t="n">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="T23" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="U23" t="n">
         <v>560</v>
@@ -2323,25 +2323,25 @@
         <v>25</v>
       </c>
       <c r="N24" t="n">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O24" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="P24" t="n">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="Q24" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="R24" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="S24" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U24" t="n">
         <v>595</v>
@@ -2481,19 +2481,19 @@
         <v>11</v>
       </c>
       <c r="N26" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O26" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P26" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="S26" t="n">
         <v>12</v>
@@ -2955,22 +2955,22 @@
         <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -3034,25 +3034,25 @@
         <v>511</v>
       </c>
       <c r="N33" t="n">
-        <v>659</v>
+        <v>579</v>
       </c>
       <c r="O33" t="n">
-        <v>649</v>
+        <v>570</v>
       </c>
       <c r="P33" t="n">
-        <v>641</v>
+        <v>563</v>
       </c>
       <c r="Q33" t="n">
-        <v>444</v>
+        <v>384</v>
       </c>
       <c r="R33" t="n">
-        <v>327</v>
+        <v>287</v>
       </c>
       <c r="S33" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="T33" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="U33" t="n">
         <v>3379</v>
@@ -3192,25 +3192,25 @@
         <v>26</v>
       </c>
       <c r="N35" t="n">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="O35" t="n">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="P35" t="n">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="Q35" t="n">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="R35" t="n">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="S35" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="T35" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="U35" t="n">
         <v>432</v>
@@ -3271,22 +3271,22 @@
         <v>5</v>
       </c>
       <c r="N36" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O36" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
@@ -3982,19 +3982,19 @@
         <v>12</v>
       </c>
       <c r="N45" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O45" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P45" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q45" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R45" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S45" t="n">
         <v>6</v>
@@ -4219,22 +4219,22 @@
         <v>2916</v>
       </c>
       <c r="N48" t="n">
-        <v>4181</v>
+        <v>4047</v>
       </c>
       <c r="O48" t="n">
-        <v>2331</v>
+        <v>2246</v>
       </c>
       <c r="P48" t="n">
-        <v>1832</v>
+        <v>1754</v>
       </c>
       <c r="Q48" t="n">
-        <v>834</v>
+        <v>792</v>
       </c>
       <c r="R48" t="n">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="S48" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
@@ -4298,25 +4298,25 @@
         <v>35</v>
       </c>
       <c r="N49" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O49" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P49" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q49" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R49" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S49" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U49" t="n">
         <v>432</v>
@@ -4377,22 +4377,22 @@
         <v>856</v>
       </c>
       <c r="N50" t="n">
-        <v>589</v>
+        <v>493</v>
       </c>
       <c r="O50" t="n">
-        <v>389</v>
+        <v>319</v>
       </c>
       <c r="P50" t="n">
-        <v>318</v>
+        <v>257</v>
       </c>
       <c r="Q50" t="n">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="R50" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="S50" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
@@ -4456,25 +4456,25 @@
         <v>8</v>
       </c>
       <c r="N51" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O51" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P51" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q51" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R51" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U51" t="n">
         <v>462</v>
@@ -4772,19 +4772,19 @@
         <v>3280</v>
       </c>
       <c r="N55" t="n">
-        <v>5208</v>
+        <v>5086</v>
       </c>
       <c r="O55" t="n">
-        <v>2528</v>
+        <v>2461</v>
       </c>
       <c r="P55" t="n">
-        <v>1852</v>
+        <v>1797</v>
       </c>
       <c r="Q55" t="n">
-        <v>714</v>
+        <v>684</v>
       </c>
       <c r="R55" t="n">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -4851,19 +4851,19 @@
         <v>860</v>
       </c>
       <c r="N56" t="n">
-        <v>2116</v>
+        <v>2071</v>
       </c>
       <c r="O56" t="n">
-        <v>785</v>
+        <v>762</v>
       </c>
       <c r="P56" t="n">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="Q56" t="n">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="R56" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="S56" t="n">
         <v>6</v>
@@ -5325,19 +5325,19 @@
         <v>7</v>
       </c>
       <c r="N62" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O62" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P62" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q62" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R62" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S62" t="n">
         <v>32</v>
@@ -5562,22 +5562,22 @@
         <v>21</v>
       </c>
       <c r="N65" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O65" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P65" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q65" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R65" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="S65" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T65" t="n">
         <v>22</v>
@@ -5799,25 +5799,25 @@
         <v>61</v>
       </c>
       <c r="N68" t="n">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="O68" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="P68" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="Q68" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="R68" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="S68" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U68" t="n">
         <v>2096</v>
@@ -5878,25 +5878,25 @@
         <v>23</v>
       </c>
       <c r="N69" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O69" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P69" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q69" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R69" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S69" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T69" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U69" t="n">
         <v>1103</v>
@@ -5957,22 +5957,22 @@
         <v>22</v>
       </c>
       <c r="N70" t="n">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="O70" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="P70" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="Q70" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="R70" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="S70" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T70" t="n">
         <v>13</v>
@@ -6036,22 +6036,22 @@
         <v>14</v>
       </c>
       <c r="N71" t="n">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O71" t="n">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="P71" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="Q71" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="R71" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="S71" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="T71" t="n">
         <v>9</v>
@@ -6352,25 +6352,25 @@
         <v>14</v>
       </c>
       <c r="N75" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="O75" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="P75" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="Q75" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="R75" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="S75" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="T75" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="U75" t="n">
         <v>1679</v>
@@ -6984,22 +6984,22 @@
         <v>87</v>
       </c>
       <c r="N83" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O83" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="P83" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Q83" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R83" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S83" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T83" t="n">
         <v>14</v>
@@ -7063,22 +7063,22 @@
         <v>10</v>
       </c>
       <c r="N84" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O84" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P84" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q84" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R84" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T84" t="n">
         <v>0</v>
@@ -7300,22 +7300,22 @@
         <v>213</v>
       </c>
       <c r="N87" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O87" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P87" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
@@ -7616,22 +7616,22 @@
         <v>203</v>
       </c>
       <c r="N91" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="O91" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P91" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="Q91" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="R91" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T91" t="n">
         <v>3</v>
@@ -7695,16 +7695,16 @@
         <v>283</v>
       </c>
       <c r="N92" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O92" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P92" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q92" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R92" t="n">
         <v>4</v>
@@ -7774,16 +7774,16 @@
         <v>42</v>
       </c>
       <c r="N93" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O93" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R93" t="n">
         <v>3</v>
@@ -8485,22 +8485,22 @@
         <v>23</v>
       </c>
       <c r="N102" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O102" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P102" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q102" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R102" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T102" t="n">
         <v>0</v>
@@ -8643,22 +8643,22 @@
         <v>600</v>
       </c>
       <c r="N104" t="n">
-        <v>4455</v>
+        <v>4356</v>
       </c>
       <c r="O104" t="n">
-        <v>2713</v>
+        <v>2632</v>
       </c>
       <c r="P104" t="n">
-        <v>2209</v>
+        <v>2133</v>
       </c>
       <c r="Q104" t="n">
-        <v>1148</v>
+        <v>1097</v>
       </c>
       <c r="R104" t="n">
-        <v>617</v>
+        <v>583</v>
       </c>
       <c r="S104" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="T104" t="n">
         <v>4</v>
@@ -8959,19 +8959,19 @@
         <v>89</v>
       </c>
       <c r="N108" t="n">
-        <v>2141</v>
+        <v>2135</v>
       </c>
       <c r="O108" t="n">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="P108" t="n">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="Q108" t="n">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="R108" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="S108" t="n">
         <v>36</v>
@@ -9038,22 +9038,22 @@
         <v>29</v>
       </c>
       <c r="N109" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="O109" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="P109" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Q109" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="R109" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T109" t="n">
         <v>0</v>
@@ -9196,16 +9196,16 @@
         <v>41</v>
       </c>
       <c r="N111" t="n">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="O111" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P111" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q111" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R111" t="n">
         <v>57</v>
@@ -9354,22 +9354,22 @@
         <v>258</v>
       </c>
       <c r="N113" t="n">
-        <v>3204</v>
+        <v>3178</v>
       </c>
       <c r="O113" t="n">
-        <v>1753</v>
+        <v>1733</v>
       </c>
       <c r="P113" t="n">
-        <v>1366</v>
+        <v>1348</v>
       </c>
       <c r="Q113" t="n">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="R113" t="n">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="S113" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="T113" t="n">
         <v>5</v>
@@ -9433,22 +9433,22 @@
         <v>82</v>
       </c>
       <c r="N114" t="n">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="O114" t="n">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="P114" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="Q114" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="R114" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T114" t="n">
         <v>0</v>
@@ -9591,16 +9591,16 @@
         <v>16</v>
       </c>
       <c r="N116" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O116" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P116" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q116" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R116" t="n">
         <v>9</v>
@@ -9670,25 +9670,25 @@
         <v>17</v>
       </c>
       <c r="N117" t="n">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="O117" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="P117" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Q117" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="R117" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="S117" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="T117" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U117" t="n">
         <v>683</v>
@@ -9828,25 +9828,25 @@
         <v>25</v>
       </c>
       <c r="N119" t="n">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="O119" t="n">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="P119" t="n">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="Q119" t="n">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="R119" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="S119" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="T119" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="U119" t="n">
         <v>2107</v>
@@ -10539,25 +10539,25 @@
         <v>131</v>
       </c>
       <c r="N128" t="n">
-        <v>2914</v>
+        <v>2879</v>
       </c>
       <c r="O128" t="n">
-        <v>1621</v>
+        <v>1591</v>
       </c>
       <c r="P128" t="n">
-        <v>1620</v>
+        <v>1590</v>
       </c>
       <c r="Q128" t="n">
-        <v>1124</v>
+        <v>1097</v>
       </c>
       <c r="R128" t="n">
-        <v>885</v>
+        <v>861</v>
       </c>
       <c r="S128" t="n">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="T128" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="U128" t="n">
         <v>13815</v>
@@ -10618,25 +10618,25 @@
         <v>6</v>
       </c>
       <c r="N129" t="n">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O129" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P129" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q129" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="R129" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="S129" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="T129" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U129" t="n">
         <v>913</v>
@@ -11250,25 +11250,25 @@
         <v>16</v>
       </c>
       <c r="N137" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O137" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P137" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q137" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R137" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="S137" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T137" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U137" t="n">
         <v>1567</v>
@@ -11566,25 +11566,25 @@
         <v>7</v>
       </c>
       <c r="N141" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O141" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P141" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q141" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R141" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U141" t="n">
         <v>27</v>
@@ -11803,22 +11803,22 @@
         <v>77</v>
       </c>
       <c r="N144" t="n">
-        <v>2848</v>
+        <v>2841</v>
       </c>
       <c r="O144" t="n">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="P144" t="n">
-        <v>1913</v>
+        <v>1908</v>
       </c>
       <c r="Q144" t="n">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="R144" t="n">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="S144" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="T144" t="n">
         <v>141</v>
@@ -11882,25 +11882,25 @@
         <v>41</v>
       </c>
       <c r="N145" t="n">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="O145" t="n">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="P145" t="n">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="Q145" t="n">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="R145" t="n">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="S145" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="T145" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="U145" t="n">
         <v>3071</v>
@@ -12277,22 +12277,22 @@
         <v>421</v>
       </c>
       <c r="N150" t="n">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="O150" t="n">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="P150" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="Q150" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="R150" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="S150" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="T150" t="n">
         <v>2</v>
@@ -12672,25 +12672,25 @@
         <v>7444</v>
       </c>
       <c r="N155" t="n">
-        <v>40287</v>
+        <v>39805</v>
       </c>
       <c r="O155" t="n">
-        <v>21842</v>
+        <v>21481</v>
       </c>
       <c r="P155" t="n">
-        <v>17003</v>
+        <v>16681</v>
       </c>
       <c r="Q155" t="n">
-        <v>8429</v>
+        <v>8197</v>
       </c>
       <c r="R155" t="n">
-        <v>4724</v>
+        <v>4558</v>
       </c>
       <c r="S155" t="n">
-        <v>1379</v>
+        <v>1317</v>
       </c>
       <c r="T155" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="U155" t="n">
         <v>219116</v>
@@ -12751,22 +12751,22 @@
         <v>133</v>
       </c>
       <c r="N156" t="n">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="O156" t="n">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P156" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="Q156" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R156" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S156" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T156" t="n">
         <v>2</v>
@@ -14695,25 +14695,25 @@
         <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="P2" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="Q2" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="R2" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="S2" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="T2" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="U2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V2" t="n">
         <v>641</v>
@@ -15283,16 +15283,16 @@
         <v>16</v>
       </c>
       <c r="O9" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -15535,25 +15535,25 @@
         <v>25</v>
       </c>
       <c r="O12" t="n">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="P12" t="n">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="Q12" t="n">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="R12" t="n">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="S12" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="T12" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="U12" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="V12" t="n">
         <v>2107</v>
@@ -15871,25 +15871,25 @@
         <v>131</v>
       </c>
       <c r="O16" t="n">
-        <v>2914</v>
+        <v>2879</v>
       </c>
       <c r="P16" t="n">
-        <v>1621</v>
+        <v>1591</v>
       </c>
       <c r="Q16" t="n">
-        <v>1620</v>
+        <v>1590</v>
       </c>
       <c r="R16" t="n">
-        <v>1124</v>
+        <v>1097</v>
       </c>
       <c r="S16" t="n">
-        <v>885</v>
+        <v>861</v>
       </c>
       <c r="T16" t="n">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="U16" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="V16" t="n">
         <v>13815</v>
@@ -15955,25 +15955,25 @@
         <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="P17" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q17" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="R17" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="S17" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="T17" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="U17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V17" t="n">
         <v>859</v>
@@ -16249,25 +16249,25 @@
         <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="P2" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q2" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="R2" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V2" t="n">
         <v>304</v>
@@ -16333,22 +16333,22 @@
         <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U3" t="n">
         <v>5</v>
@@ -16417,25 +16417,25 @@
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>62</v>
@@ -16501,19 +16501,19 @@
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
@@ -16669,25 +16669,25 @@
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="P7" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V7" t="n">
         <v>59</v>
@@ -16753,25 +16753,25 @@
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="R8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V8" t="n">
         <v>58</v>
@@ -17005,25 +17005,25 @@
         <v>481</v>
       </c>
       <c r="O11" t="n">
-        <v>2175</v>
+        <v>2005</v>
       </c>
       <c r="P11" t="n">
-        <v>1786</v>
+        <v>1623</v>
       </c>
       <c r="Q11" t="n">
-        <v>1620</v>
+        <v>1462</v>
       </c>
       <c r="R11" t="n">
-        <v>1192</v>
+        <v>1057</v>
       </c>
       <c r="S11" t="n">
-        <v>860</v>
+        <v>742</v>
       </c>
       <c r="T11" t="n">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="U11" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="V11" t="n">
         <v>3950</v>
@@ -17089,25 +17089,25 @@
         <v>58</v>
       </c>
       <c r="O12" t="n">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="P12" t="n">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="Q12" t="n">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="R12" t="n">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="S12" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="U12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V12" t="n">
         <v>458</v>
@@ -17173,25 +17173,25 @@
         <v>1985</v>
       </c>
       <c r="O13" t="n">
-        <v>8244</v>
+        <v>7656</v>
       </c>
       <c r="P13" t="n">
-        <v>7089</v>
+        <v>6527</v>
       </c>
       <c r="Q13" t="n">
-        <v>6599</v>
+        <v>6048</v>
       </c>
       <c r="R13" t="n">
-        <v>5086</v>
+        <v>4607</v>
       </c>
       <c r="S13" t="n">
-        <v>3875</v>
+        <v>3438</v>
       </c>
       <c r="T13" t="n">
-        <v>1813</v>
+        <v>1505</v>
       </c>
       <c r="U13" t="n">
-        <v>482</v>
+        <v>348</v>
       </c>
       <c r="V13" t="n">
         <v>14134</v>
@@ -17341,22 +17341,22 @@
         <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q15" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="R15" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U15" t="n">
         <v>7</v>
@@ -17929,25 +17929,25 @@
         <v>34</v>
       </c>
       <c r="O22" t="n">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="P22" t="n">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="Q22" t="n">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="R22" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="S22" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="T22" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="U22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22" t="n">
         <v>451</v>
@@ -18013,25 +18013,25 @@
         <v>26</v>
       </c>
       <c r="O23" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="P23" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="Q23" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="R23" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="S23" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="T23" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="U23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
         <v>172</v>
@@ -18097,25 +18097,25 @@
         <v>20</v>
       </c>
       <c r="O24" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="P24" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="Q24" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="R24" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="S24" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="T24" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="U24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24" t="n">
         <v>244</v>
@@ -18181,25 +18181,25 @@
         <v>104</v>
       </c>
       <c r="O25" t="n">
-        <v>523</v>
+        <v>461</v>
       </c>
       <c r="P25" t="n">
-        <v>450</v>
+        <v>391</v>
       </c>
       <c r="Q25" t="n">
-        <v>427</v>
+        <v>369</v>
       </c>
       <c r="R25" t="n">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="S25" t="n">
-        <v>282</v>
+        <v>232</v>
       </c>
       <c r="T25" t="n">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="U25" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="V25" t="n">
         <v>775</v>
@@ -18265,25 +18265,25 @@
         <v>14</v>
       </c>
       <c r="O26" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P26" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q26" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="R26" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="S26" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="T26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26" t="n">
         <v>312</v>
@@ -18601,16 +18601,16 @@
         <v>9</v>
       </c>
       <c r="O30" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P30" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q30" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R30" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S30" t="n">
         <v>53</v>
@@ -18685,25 +18685,25 @@
         <v>9</v>
       </c>
       <c r="O31" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="P31" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="Q31" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R31" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="S31" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T31" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="U31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V31" t="n">
         <v>576</v>
@@ -18769,25 +18769,25 @@
         <v>25</v>
       </c>
       <c r="O32" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="P32" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="Q32" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="R32" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="S32" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="T32" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="U32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V32" t="n">
         <v>111</v>
@@ -18937,25 +18937,25 @@
         <v>31</v>
       </c>
       <c r="O34" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="P34" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="Q34" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="R34" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="S34" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="T34" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="U34" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="V34" t="n">
         <v>327</v>
@@ -19021,25 +19021,25 @@
         <v>108</v>
       </c>
       <c r="O35" t="n">
-        <v>647</v>
+        <v>614</v>
       </c>
       <c r="P35" t="n">
-        <v>563</v>
+        <v>532</v>
       </c>
       <c r="Q35" t="n">
-        <v>527</v>
+        <v>497</v>
       </c>
       <c r="R35" t="n">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="S35" t="n">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="T35" t="n">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="U35" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="V35" t="n">
         <v>1100</v>
@@ -19273,25 +19273,25 @@
         <v>32</v>
       </c>
       <c r="O38" t="n">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="P38" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="Q38" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="R38" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="S38" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T38" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="U38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
         <v>425</v>
@@ -19357,22 +19357,22 @@
         <v>20</v>
       </c>
       <c r="O39" t="n">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="P39" t="n">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="Q39" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="R39" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="S39" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="T39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U39" t="n">
         <v>11</v>
@@ -19441,19 +19441,19 @@
         <v>11</v>
       </c>
       <c r="O40" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P40" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="Q40" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="R40" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="S40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T40" t="n">
         <v>12</v>
@@ -19693,7 +19693,7 @@
         <v>3</v>
       </c>
       <c r="O43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P43" t="n">
         <v>4</v>
@@ -19777,25 +19777,25 @@
         <v>69</v>
       </c>
       <c r="O44" t="n">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="P44" t="n">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="Q44" t="n">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="R44" t="n">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="S44" t="n">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="T44" t="n">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="U44" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="V44" t="n">
         <v>560</v>
@@ -20029,19 +20029,19 @@
         <v>13</v>
       </c>
       <c r="O47" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="P47" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q47" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R47" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S47" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="T47" t="n">
         <v>16</v>
@@ -20575,25 +20575,25 @@
         <v>27</v>
       </c>
       <c r="O2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P2" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q2" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R2" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S2" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" t="n">
         <v>377</v>
@@ -20659,25 +20659,25 @@
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P3" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q3" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="R3" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="S3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V3" t="n">
         <v>462</v>
@@ -20911,22 +20911,22 @@
         <v>2916</v>
       </c>
       <c r="O6" t="n">
-        <v>4181</v>
+        <v>4047</v>
       </c>
       <c r="P6" t="n">
-        <v>2331</v>
+        <v>2246</v>
       </c>
       <c r="Q6" t="n">
-        <v>1832</v>
+        <v>1754</v>
       </c>
       <c r="R6" t="n">
-        <v>834</v>
+        <v>792</v>
       </c>
       <c r="S6" t="n">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="T6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
@@ -20995,22 +20995,22 @@
         <v>856</v>
       </c>
       <c r="O7" t="n">
-        <v>589</v>
+        <v>493</v>
       </c>
       <c r="P7" t="n">
-        <v>389</v>
+        <v>319</v>
       </c>
       <c r="Q7" t="n">
-        <v>318</v>
+        <v>257</v>
       </c>
       <c r="R7" t="n">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="S7" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="T7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -21247,19 +21247,19 @@
         <v>3280</v>
       </c>
       <c r="O10" t="n">
-        <v>5208</v>
+        <v>5086</v>
       </c>
       <c r="P10" t="n">
-        <v>2528</v>
+        <v>2461</v>
       </c>
       <c r="Q10" t="n">
-        <v>1852</v>
+        <v>1797</v>
       </c>
       <c r="R10" t="n">
-        <v>714</v>
+        <v>684</v>
       </c>
       <c r="S10" t="n">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="T10" t="n">
         <v>15</v>
@@ -21331,19 +21331,19 @@
         <v>860</v>
       </c>
       <c r="O11" t="n">
-        <v>2116</v>
+        <v>2071</v>
       </c>
       <c r="P11" t="n">
-        <v>785</v>
+        <v>762</v>
       </c>
       <c r="Q11" t="n">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="R11" t="n">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="S11" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="T11" t="n">
         <v>6</v>
@@ -21415,19 +21415,19 @@
         <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P12" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T12" t="n">
         <v>6</v>
@@ -22381,25 +22381,25 @@
         <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
         <v>401</v>
@@ -23053,22 +23053,22 @@
         <v>21</v>
       </c>
       <c r="O16" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P16" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Q16" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="R16" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="S16" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="T16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U16" t="n">
         <v>22</v>
@@ -24397,19 +24397,19 @@
         <v>7</v>
       </c>
       <c r="O32" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P32" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q32" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R32" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S32" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T32" t="n">
         <v>32</v>
@@ -24733,25 +24733,25 @@
         <v>61</v>
       </c>
       <c r="O36" t="n">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="P36" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="R36" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="S36" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="T36" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="U36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V36" t="n">
         <v>2096</v>
@@ -24901,22 +24901,22 @@
         <v>22</v>
       </c>
       <c r="O38" t="n">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="P38" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="Q38" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="R38" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="S38" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="T38" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="U38" t="n">
         <v>13</v>
@@ -24985,22 +24985,22 @@
         <v>13</v>
       </c>
       <c r="O39" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P39" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q39" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="R39" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="S39" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T39" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U39" t="n">
         <v>8</v>
@@ -26371,13 +26371,13 @@
         <v>42</v>
       </c>
       <c r="O8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R8" t="n">
         <v>11</v>
@@ -26539,22 +26539,22 @@
         <v>203</v>
       </c>
       <c r="O10" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="P10" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="Q10" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="R10" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S10" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="T10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U10" t="n">
         <v>3</v>
@@ -27295,22 +27295,22 @@
         <v>213</v>
       </c>
       <c r="O19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>1</v>
@@ -27631,16 +27631,16 @@
         <v>283</v>
       </c>
       <c r="O23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -27715,16 +27715,16 @@
         <v>42</v>
       </c>
       <c r="O24" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -28135,22 +28135,22 @@
         <v>28</v>
       </c>
       <c r="O29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29" t="n">
         <v>3</v>
@@ -28219,22 +28219,22 @@
         <v>9</v>
       </c>
       <c r="O30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -28513,22 +28513,22 @@
         <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P3" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -28765,22 +28765,22 @@
         <v>600</v>
       </c>
       <c r="O6" t="n">
-        <v>4455</v>
+        <v>4356</v>
       </c>
       <c r="P6" t="n">
-        <v>2713</v>
+        <v>2632</v>
       </c>
       <c r="Q6" t="n">
-        <v>2209</v>
+        <v>2133</v>
       </c>
       <c r="R6" t="n">
-        <v>1148</v>
+        <v>1097</v>
       </c>
       <c r="S6" t="n">
-        <v>617</v>
+        <v>583</v>
       </c>
       <c r="T6" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="U6" t="n">
         <v>4</v>
@@ -29017,19 +29017,19 @@
         <v>89</v>
       </c>
       <c r="O9" t="n">
-        <v>2141</v>
+        <v>2135</v>
       </c>
       <c r="P9" t="n">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="Q9" t="n">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="R9" t="n">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="S9" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="T9" t="n">
         <v>36</v>
@@ -29101,22 +29101,22 @@
         <v>29</v>
       </c>
       <c r="O10" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P10" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q10" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -29185,16 +29185,16 @@
         <v>41</v>
       </c>
       <c r="O11" t="n">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="P11" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Q11" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="R11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S11" t="n">
         <v>57</v>
@@ -29353,22 +29353,22 @@
         <v>258</v>
       </c>
       <c r="O13" t="n">
-        <v>3204</v>
+        <v>3178</v>
       </c>
       <c r="P13" t="n">
-        <v>1753</v>
+        <v>1733</v>
       </c>
       <c r="Q13" t="n">
-        <v>1366</v>
+        <v>1348</v>
       </c>
       <c r="R13" t="n">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="S13" t="n">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="T13" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U13" t="n">
         <v>5</v>
@@ -29437,22 +29437,22 @@
         <v>82</v>
       </c>
       <c r="O14" t="n">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="P14" t="n">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="Q14" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="R14" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="S14" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="T14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -31075,25 +31075,25 @@
         <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P18" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q18" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R18" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>1143</v>
@@ -31411,25 +31411,25 @@
         <v>7</v>
       </c>
       <c r="O22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
         <v>27</v>
@@ -31663,22 +31663,22 @@
         <v>77</v>
       </c>
       <c r="O25" t="n">
-        <v>2848</v>
+        <v>2841</v>
       </c>
       <c r="P25" t="n">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="Q25" t="n">
-        <v>1913</v>
+        <v>1908</v>
       </c>
       <c r="R25" t="n">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="S25" t="n">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="T25" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="U25" t="n">
         <v>141</v>
@@ -31747,25 +31747,25 @@
         <v>41</v>
       </c>
       <c r="O26" t="n">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="P26" t="n">
-        <v>892</v>
+        <v>885</v>
       </c>
       <c r="Q26" t="n">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="R26" t="n">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="S26" t="n">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="T26" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="U26" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="V26" t="n">
         <v>3071</v>
@@ -31999,22 +31999,22 @@
         <v>421</v>
       </c>
       <c r="O29" t="n">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="P29" t="n">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="Q29" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="R29" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="S29" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="T29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U29" t="n">
         <v>2</v>
@@ -32251,25 +32251,25 @@
         <v>7444</v>
       </c>
       <c r="O32" t="n">
-        <v>40287</v>
+        <v>39805</v>
       </c>
       <c r="P32" t="n">
-        <v>21842</v>
+        <v>21481</v>
       </c>
       <c r="Q32" t="n">
-        <v>17003</v>
+        <v>16681</v>
       </c>
       <c r="R32" t="n">
-        <v>8429</v>
+        <v>8197</v>
       </c>
       <c r="S32" t="n">
-        <v>4724</v>
+        <v>4558</v>
       </c>
       <c r="T32" t="n">
-        <v>1379</v>
+        <v>1317</v>
       </c>
       <c r="U32" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="V32" t="n">
         <v>219116</v>
@@ -32335,22 +32335,22 @@
         <v>133</v>
       </c>
       <c r="O33" t="n">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="P33" t="n">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="Q33" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="R33" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S33" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="T33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="U33" t="n">
         <v>2</v>

--- a/summary_stats/chuuchuu_summary_2025_03.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_03.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U178"/>
+  <dimension ref="A1:U177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -664,28 +664,28 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="O3" t="n">
+        <v>24</v>
+      </c>
+      <c r="P3" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>19</v>
+      </c>
+      <c r="R3" t="n">
+        <v>17</v>
+      </c>
+      <c r="S3" t="n">
         <v>7</v>
       </c>
-      <c r="P3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3</v>
-      </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>61</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4">
@@ -1916,40 +1916,40 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3468</v>
+        <v>3482</v>
       </c>
       <c r="K19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L19" t="n">
         <v>259</v>
       </c>
       <c r="M19" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N19" t="n">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="O19" t="n">
-        <v>1525</v>
+        <v>1498</v>
       </c>
       <c r="P19" t="n">
-        <v>1425</v>
+        <v>1401</v>
       </c>
       <c r="Q19" t="n">
-        <v>1051</v>
+        <v>1031</v>
       </c>
       <c r="R19" t="n">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="S19" t="n">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="T19" t="n">
         <v>113</v>
       </c>
       <c r="U19" t="n">
-        <v>3337</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="20">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2469,40 +2469,40 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N26" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="O26" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="P26" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="Q26" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="R26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27">
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>3455</v>
+        <v>3456</v>
       </c>
       <c r="K33" t="n">
         <v>104</v>
@@ -3034,28 +3034,28 @@
         <v>485</v>
       </c>
       <c r="N33" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O33" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P33" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Q33" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R33" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T33" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U33" t="n">
-        <v>3199</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="34">
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -4219,16 +4219,16 @@
         <v>2915</v>
       </c>
       <c r="N48" t="n">
-        <v>4045</v>
+        <v>4049</v>
       </c>
       <c r="O48" t="n">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="P48" t="n">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="Q48" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="R48" t="n">
         <v>335</v>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>3008</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="51">
@@ -4772,13 +4772,13 @@
         <v>3280</v>
       </c>
       <c r="N55" t="n">
-        <v>5086</v>
+        <v>5085</v>
       </c>
       <c r="O55" t="n">
         <v>2461</v>
       </c>
       <c r="P55" t="n">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="Q55" t="n">
         <v>684</v>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1687</v>
+        <v>1748</v>
       </c>
       <c r="K76" t="n">
         <v>6</v>
@@ -6431,28 +6431,28 @@
         <v>14</v>
       </c>
       <c r="N76" t="n">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="O76" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="P76" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="Q76" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="R76" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="S76" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="T76" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="U76" t="n">
-        <v>1679</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="77">
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -7501,17 +7501,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -7525,40 +7525,40 @@
         </is>
       </c>
       <c r="J90" t="n">
+        <v>57</v>
+      </c>
+      <c r="K90" t="n">
         <v>1</v>
       </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" t="n">
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="91">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7604,40 +7604,40 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>57</v>
+        <v>1134</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U91" t="n">
-        <v>56</v>
+        <v>991</v>
       </c>
     </row>
     <row r="92">
@@ -7659,17 +7659,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7683,40 +7683,40 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>1135</v>
+        <v>13225</v>
       </c>
       <c r="K92" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L92" t="n">
-        <v>151</v>
+        <v>242</v>
       </c>
       <c r="M92" t="n">
-        <v>199</v>
+        <v>283</v>
       </c>
       <c r="N92" t="n">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="O92" t="n">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="P92" t="n">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="Q92" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="R92" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="S92" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="T92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>992</v>
+        <v>13018</v>
       </c>
     </row>
     <row r="93">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7762,40 +7762,40 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>13225</v>
+        <v>1046</v>
       </c>
       <c r="K93" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>242</v>
+        <v>42</v>
       </c>
       <c r="M93" t="n">
-        <v>283</v>
+        <v>42</v>
       </c>
       <c r="N93" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O93" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="P93" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
         <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>13018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="94">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7841,31 +7841,31 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>1046</v>
+        <v>4</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -7874,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>1017</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -7896,17 +7896,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>LYRIA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
         <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="96">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7999,40 +7999,40 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>52</v>
+        <v>844</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U96" t="n">
-        <v>52</v>
+        <v>837</v>
       </c>
     </row>
     <row r="97">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8078,40 +8078,40 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>835</v>
+        <v>3</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -8133,17 +8133,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>LYRIA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -8153,44 +8153,44 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>13</v>
+        <v>268</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
     </row>
     <row r="99">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>RJX</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -8232,44 +8232,44 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>268</v>
+        <v>372</v>
       </c>
       <c r="K99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M99" t="n">
+        <v>3</v>
+      </c>
+      <c r="N99" t="n">
+        <v>26</v>
+      </c>
+      <c r="O99" t="n">
+        <v>19</v>
+      </c>
+      <c r="P99" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>11</v>
+      </c>
+      <c r="R99" t="n">
+        <v>10</v>
+      </c>
+      <c r="S99" t="n">
         <v>6</v>
       </c>
-      <c r="N99" t="n">
-        <v>74</v>
-      </c>
-      <c r="O99" t="n">
-        <v>60</v>
-      </c>
-      <c r="P99" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>51</v>
-      </c>
-      <c r="R99" t="n">
-        <v>41</v>
-      </c>
-      <c r="S99" t="n">
-        <v>34</v>
-      </c>
       <c r="T99" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>262</v>
+        <v>371</v>
       </c>
     </row>
     <row r="100">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RJX</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -8311,44 +8311,44 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>372</v>
+        <v>54</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O100" t="n">
+        <v>20</v>
+      </c>
+      <c r="P100" t="n">
         <v>19</v>
       </c>
-      <c r="P100" t="n">
+      <c r="Q100" t="n">
         <v>18</v>
       </c>
-      <c r="Q100" t="n">
-        <v>11</v>
-      </c>
       <c r="R100" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U100" t="n">
-        <v>371</v>
+        <v>54</v>
       </c>
     </row>
     <row r="101">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8390,11 +8390,11 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -8406,28 +8406,28 @@
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="O101" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="R101" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>EUROCITY</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -8473,40 +8473,40 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>4</v>
+        <v>778</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N102" t="n">
-        <v>2</v>
+        <v>191</v>
       </c>
       <c r="O102" t="n">
+        <v>117</v>
+      </c>
+      <c r="P102" t="n">
+        <v>99</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>46</v>
+      </c>
+      <c r="R102" t="n">
+        <v>26</v>
+      </c>
+      <c r="S102" t="n">
+        <v>7</v>
+      </c>
+      <c r="T102" t="n">
         <v>1</v>
       </c>
-      <c r="P102" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>1</v>
-      </c>
-      <c r="R102" t="n">
-        <v>1</v>
-      </c>
-      <c r="S102" t="n">
-        <v>1</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
       <c r="U102" t="n">
-        <v>4</v>
+        <v>759</v>
       </c>
     </row>
     <row r="103">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>EUROCITY</t>
+          <t>EUROCITY DIRECT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8552,40 +8552,40 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>778</v>
+        <v>723</v>
       </c>
       <c r="K103" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L103" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M103" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="N103" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="O103" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="P103" t="n">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="Q103" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="R103" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="T103" t="n">
         <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>759</v>
+        <v>719</v>
       </c>
     </row>
     <row r="104">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>EUROCITY DIRECT</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -8631,40 +8631,40 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>723</v>
+        <v>24512</v>
       </c>
       <c r="K104" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="L104" t="n">
-        <v>2</v>
+        <v>526</v>
       </c>
       <c r="M104" t="n">
+        <v>602</v>
+      </c>
+      <c r="N104" t="n">
+        <v>4356</v>
+      </c>
+      <c r="O104" t="n">
+        <v>2632</v>
+      </c>
+      <c r="P104" t="n">
+        <v>2133</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1098</v>
+      </c>
+      <c r="R104" t="n">
+        <v>583</v>
+      </c>
+      <c r="S104" t="n">
+        <v>110</v>
+      </c>
+      <c r="T104" t="n">
         <v>5</v>
       </c>
-      <c r="N104" t="n">
-        <v>201</v>
-      </c>
-      <c r="O104" t="n">
-        <v>131</v>
-      </c>
-      <c r="P104" t="n">
-        <v>117</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>66</v>
-      </c>
-      <c r="R104" t="n">
-        <v>42</v>
-      </c>
-      <c r="S104" t="n">
-        <v>17</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
       <c r="U104" t="n">
-        <v>719</v>
+        <v>24140</v>
       </c>
     </row>
     <row r="105">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -8710,40 +8710,40 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>24510</v>
+        <v>2767</v>
       </c>
       <c r="K105" t="n">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="L105" t="n">
-        <v>525</v>
+        <v>11</v>
       </c>
       <c r="M105" t="n">
-        <v>600</v>
+        <v>27</v>
       </c>
       <c r="N105" t="n">
-        <v>4356</v>
+        <v>361</v>
       </c>
       <c r="O105" t="n">
-        <v>2632</v>
+        <v>216</v>
       </c>
       <c r="P105" t="n">
-        <v>2133</v>
+        <v>180</v>
       </c>
       <c r="Q105" t="n">
-        <v>1097</v>
+        <v>85</v>
       </c>
       <c r="R105" t="n">
-        <v>583</v>
+        <v>50</v>
       </c>
       <c r="S105" t="n">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="T105" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U105" t="n">
-        <v>24139</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="106">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8789,40 +8789,40 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>2767</v>
+        <v>4</v>
       </c>
       <c r="K106" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L106" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="N106" t="n">
-        <v>361</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T106" t="n">
         <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>2743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -8844,17 +8844,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8868,40 +8868,40 @@
         </is>
       </c>
       <c r="J107" t="n">
+        <v>446</v>
+      </c>
+      <c r="K107" t="n">
+        <v>13</v>
+      </c>
+      <c r="L107" t="n">
         <v>1</v>
       </c>
-      <c r="K107" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
       <c r="M107" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
     </row>
     <row r="108">
@@ -8923,22 +8923,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>L</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8947,40 +8947,40 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>446</v>
+        <v>14920</v>
       </c>
       <c r="K108" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L108" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="M108" t="n">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="N108" t="n">
-        <v>200</v>
+        <v>2135</v>
       </c>
       <c r="O108" t="n">
-        <v>147</v>
+        <v>1138</v>
       </c>
       <c r="P108" t="n">
-        <v>122</v>
+        <v>841</v>
       </c>
       <c r="Q108" t="n">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="R108" t="n">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="S108" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="T108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U108" t="n">
-        <v>433</v>
+        <v>14852</v>
       </c>
     </row>
     <row r="109">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9026,40 +9026,40 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>14920</v>
+        <v>3797</v>
       </c>
       <c r="K109" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L109" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="M109" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="N109" t="n">
-        <v>2135</v>
+        <v>236</v>
       </c>
       <c r="O109" t="n">
-        <v>1138</v>
+        <v>132</v>
       </c>
       <c r="P109" t="n">
-        <v>841</v>
+        <v>101</v>
       </c>
       <c r="Q109" t="n">
-        <v>373</v>
+        <v>45</v>
       </c>
       <c r="R109" t="n">
-        <v>188</v>
+        <v>19</v>
       </c>
       <c r="S109" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="T109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
-        <v>14852</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="110">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -9096,49 +9096,49 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>3797</v>
+        <v>47</v>
       </c>
       <c r="K110" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="N110" t="n">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="O110" t="n">
-        <v>132</v>
+        <v>6</v>
       </c>
       <c r="P110" t="n">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="Q110" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="R110" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="S110" t="n">
         <v>1</v>
       </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U110" t="n">
-        <v>3784</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>P</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9175,49 +9175,49 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>47</v>
+        <v>3595</v>
       </c>
       <c r="K111" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M111" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="N111" t="n">
-        <v>11</v>
+        <v>677</v>
       </c>
       <c r="O111" t="n">
-        <v>6</v>
+        <v>398</v>
       </c>
       <c r="P111" t="n">
-        <v>6</v>
+        <v>308</v>
       </c>
       <c r="Q111" t="n">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="R111" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="S111" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T111" t="n">
         <v>1</v>
       </c>
       <c r="U111" t="n">
-        <v>36</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="112">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9263,40 +9263,40 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>3595</v>
+        <v>205</v>
       </c>
       <c r="K112" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>677</v>
+        <v>19</v>
       </c>
       <c r="O112" t="n">
-        <v>398</v>
+        <v>9</v>
       </c>
       <c r="P112" t="n">
-        <v>308</v>
+        <v>9</v>
       </c>
       <c r="Q112" t="n">
-        <v>135</v>
+        <v>3</v>
       </c>
       <c r="R112" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="S112" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U112" t="n">
-        <v>3560</v>
+        <v>205</v>
       </c>
     </row>
     <row r="113">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>S</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -9342,40 +9342,40 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>205</v>
+        <v>22251</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L113" t="n">
-        <v>1</v>
+        <v>191</v>
       </c>
       <c r="M113" t="n">
-        <v>1</v>
+        <v>258</v>
       </c>
       <c r="N113" t="n">
-        <v>19</v>
+        <v>3176</v>
       </c>
       <c r="O113" t="n">
-        <v>9</v>
+        <v>1733</v>
       </c>
       <c r="P113" t="n">
-        <v>9</v>
+        <v>1348</v>
       </c>
       <c r="Q113" t="n">
-        <v>3</v>
+        <v>631</v>
       </c>
       <c r="R113" t="n">
-        <v>2</v>
+        <v>307</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U113" t="n">
-        <v>205</v>
+        <v>22052</v>
       </c>
     </row>
     <row r="114">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -9421,40 +9421,40 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>22251</v>
+        <v>2983</v>
       </c>
       <c r="K114" t="n">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="L114" t="n">
-        <v>191</v>
+        <v>62</v>
       </c>
       <c r="M114" t="n">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="N114" t="n">
-        <v>3178</v>
+        <v>697</v>
       </c>
       <c r="O114" t="n">
-        <v>1733</v>
+        <v>420</v>
       </c>
       <c r="P114" t="n">
-        <v>1348</v>
+        <v>319</v>
       </c>
       <c r="Q114" t="n">
-        <v>631</v>
+        <v>140</v>
       </c>
       <c r="R114" t="n">
-        <v>307</v>
+        <v>54</v>
       </c>
       <c r="S114" t="n">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="T114" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>22052</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="115">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>TGV INOUI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -9500,40 +9500,40 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>2982</v>
+        <v>332</v>
       </c>
       <c r="K115" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L115" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>696</v>
+        <v>141</v>
       </c>
       <c r="O115" t="n">
-        <v>419</v>
+        <v>103</v>
       </c>
       <c r="P115" t="n">
-        <v>318</v>
+        <v>103</v>
       </c>
       <c r="Q115" t="n">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="R115" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="S115" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U115" t="n">
-        <v>2921</v>
+        <v>331</v>
       </c>
     </row>
     <row r="116">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>TGV INOUI</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -9579,40 +9579,40 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>162</v>
+        <v>1574</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N116" t="n">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="O116" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="P116" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="Q116" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="R116" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="S116" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>162</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="117">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -9658,40 +9658,40 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>1574</v>
+        <v>711</v>
       </c>
       <c r="K117" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L117" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M117" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N117" t="n">
-        <v>101</v>
+        <v>243</v>
       </c>
       <c r="O117" t="n">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="P117" t="n">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="Q117" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="R117" t="n">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="T117" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U117" t="n">
-        <v>1572</v>
+        <v>701</v>
       </c>
     </row>
     <row r="118">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -9737,40 +9737,40 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>692</v>
+        <v>2</v>
       </c>
       <c r="K118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -9792,17 +9792,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>INTERCITES</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9816,40 +9816,40 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>2</v>
+        <v>2141</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="U119" t="n">
-        <v>0</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="120">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -9895,40 +9895,40 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>2122</v>
+        <v>8</v>
       </c>
       <c r="K120" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>557</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>2107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>INTERCITES</t>
+          <t>INTERCITES DE NUIT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9970,44 +9970,44 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
     </row>
     <row r="122">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10053,40 +10053,40 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="K122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -10108,17 +10108,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>INTERCITES DE NUIT</t>
+          <t>LYRIA</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -10128,11 +10128,11 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="U123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -10211,40 +10211,40 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>2</v>
+        <v>1009</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N124" t="n">
-        <v>1</v>
+        <v>241</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="U124" t="n">
-        <v>2</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="125">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -10290,40 +10290,40 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="U125" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -10345,17 +10345,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LYRIA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -10365,35 +10365,35 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -10402,7 +10402,7 @@
         <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="127">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>TGV</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -10444,35 +10444,35 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="K127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N127" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -10481,7 +10481,7 @@
         <v>0</v>
       </c>
       <c r="U127" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>TGV</t>
+          <t>TGV INOUI</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -10527,40 +10527,40 @@
         </is>
       </c>
       <c r="J128" t="n">
+        <v>14373</v>
+      </c>
+      <c r="K128" t="n">
         <v>36</v>
       </c>
-      <c r="K128" t="n">
-        <v>1</v>
-      </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M128" t="n">
-        <v>1</v>
+        <v>151</v>
       </c>
       <c r="N128" t="n">
-        <v>18</v>
+        <v>3204</v>
       </c>
       <c r="O128" t="n">
-        <v>10</v>
+        <v>1841</v>
       </c>
       <c r="P128" t="n">
-        <v>9</v>
+        <v>1840</v>
       </c>
       <c r="Q128" t="n">
-        <v>5</v>
+        <v>1249</v>
       </c>
       <c r="R128" t="n">
-        <v>2</v>
+        <v>964</v>
       </c>
       <c r="S128" t="n">
-        <v>0</v>
+        <v>474</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="U128" t="n">
-        <v>35</v>
+        <v>14301</v>
       </c>
     </row>
     <row r="129">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -10606,40 +10606,40 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>13799</v>
+        <v>1229</v>
       </c>
       <c r="K129" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="M129" t="n">
-        <v>131</v>
+        <v>7</v>
       </c>
       <c r="N129" t="n">
-        <v>2856</v>
+        <v>401</v>
       </c>
       <c r="O129" t="n">
-        <v>1575</v>
+        <v>245</v>
       </c>
       <c r="P129" t="n">
-        <v>1574</v>
+        <v>245</v>
       </c>
       <c r="Q129" t="n">
-        <v>1085</v>
+        <v>191</v>
       </c>
       <c r="R129" t="n">
-        <v>853</v>
+        <v>144</v>
       </c>
       <c r="S129" t="n">
-        <v>407</v>
+        <v>62</v>
       </c>
       <c r="T129" t="n">
-        <v>160</v>
+        <v>18</v>
       </c>
       <c r="U129" t="n">
-        <v>13734</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="130">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -10685,40 +10685,40 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>913</v>
+        <v>153</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="U130" t="n">
-        <v>913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10740,22 +10740,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>TGV INOUI</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -10764,40 +10764,40 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>1033</v>
+        <v>713</v>
       </c>
       <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>12</v>
+      </c>
+      <c r="O131" t="n">
+        <v>10</v>
+      </c>
+      <c r="P131" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q131" t="n">
         <v>7</v>
       </c>
-      <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="n">
-        <v>7</v>
-      </c>
-      <c r="N131" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T131" t="n">
         <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>713</v>
       </c>
     </row>
     <row r="132">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>713</v>
+        <v>56</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -10855,28 +10855,28 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O132" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P132" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q132" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T132" t="n">
         <v>0</v>
       </c>
       <c r="U132" t="n">
-        <v>713</v>
+        <v>56</v>
       </c>
     </row>
     <row r="133">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -10913,16 +10913,16 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -10934,28 +10934,28 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
+        <v>6</v>
+      </c>
+      <c r="O133" t="n">
+        <v>5</v>
+      </c>
+      <c r="P133" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>3</v>
+      </c>
+      <c r="R133" t="n">
+        <v>3</v>
+      </c>
+      <c r="S133" t="n">
         <v>1</v>
       </c>
-      <c r="O133" t="n">
-        <v>1</v>
-      </c>
-      <c r="P133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
       <c r="T133" t="n">
         <v>0</v>
       </c>
       <c r="U133" t="n">
-        <v>56</v>
+        <v>124</v>
       </c>
     </row>
     <row r="134">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -10992,16 +10992,16 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -11013,28 +11013,28 @@
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O134" t="n">
+        <v>8</v>
+      </c>
+      <c r="P134" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q134" t="n">
         <v>5</v>
       </c>
-      <c r="P134" t="n">
+      <c r="R134" t="n">
         <v>5</v>
       </c>
-      <c r="Q134" t="n">
-        <v>3</v>
-      </c>
-      <c r="R134" t="n">
-        <v>3</v>
-      </c>
       <c r="S134" t="n">
+        <v>3</v>
+      </c>
+      <c r="T134" t="n">
         <v>1</v>
       </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
       <c r="U134" t="n">
-        <v>124</v>
+        <v>62</v>
       </c>
     </row>
     <row r="135">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -11080,7 +11080,7 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -11092,28 +11092,28 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="O135" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P135" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q135" t="n">
         <v>5</v>
       </c>
       <c r="R135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
-        <v>62</v>
+        <v>124</v>
       </c>
     </row>
     <row r="136">
@@ -11135,12 +11135,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -11159,31 +11159,31 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N136" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -11192,7 +11192,7 @@
         <v>0</v>
       </c>
       <c r="U136" t="n">
-        <v>124</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -11238,40 +11238,40 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>5</v>
+        <v>1582</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L137" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M137" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U137" t="n">
-        <v>3</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="138">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ECE</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -11317,40 +11317,40 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>1582</v>
+        <v>2</v>
       </c>
       <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>1</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
         <v>2</v>
-      </c>
-      <c r="L138" t="n">
-        <v>14</v>
-      </c>
-      <c r="M138" t="n">
-        <v>16</v>
-      </c>
-      <c r="N138" t="n">
-        <v>435</v>
-      </c>
-      <c r="O138" t="n">
-        <v>321</v>
-      </c>
-      <c r="P138" t="n">
-        <v>276</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>169</v>
-      </c>
-      <c r="R138" t="n">
-        <v>116</v>
-      </c>
-      <c r="S138" t="n">
-        <v>44</v>
-      </c>
-      <c r="T138" t="n">
-        <v>12</v>
-      </c>
-      <c r="U138" t="n">
-        <v>1567</v>
       </c>
     </row>
     <row r="139">
@@ -11372,12 +11372,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -11392,11 +11392,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -11408,28 +11408,28 @@
         <v>0</v>
       </c>
       <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
         <v>1</v>
-      </c>
-      <c r="O139" t="n">
-        <v>1</v>
-      </c>
-      <c r="P139" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>1</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -11475,31 +11475,31 @@
         </is>
       </c>
       <c r="J140" t="n">
+        <v>29</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>24</v>
+      </c>
+      <c r="M140" t="n">
+        <v>24</v>
+      </c>
+      <c r="N140" t="n">
         <v>1</v>
       </c>
-      <c r="K140" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="n">
-        <v>0</v>
-      </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -11508,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="U140" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -11550,44 +11550,44 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J141" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="M141" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="N141" t="n">
+        <v>9</v>
+      </c>
+      <c r="O141" t="n">
+        <v>8</v>
+      </c>
+      <c r="P141" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>6</v>
+      </c>
+      <c r="R141" t="n">
+        <v>3</v>
+      </c>
+      <c r="S141" t="n">
+        <v>2</v>
+      </c>
+      <c r="T141" t="n">
         <v>1</v>
       </c>
-      <c r="O141" t="n">
-        <v>1</v>
-      </c>
-      <c r="P141" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>1</v>
-      </c>
-      <c r="R141" t="n">
-        <v>1</v>
-      </c>
-      <c r="S141" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" t="n">
-        <v>0</v>
-      </c>
       <c r="U141" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="142">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>EXP</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>31</v>
+        <v>501</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -11645,28 +11645,28 @@
         <v>7</v>
       </c>
       <c r="N142" t="n">
+        <v>254</v>
+      </c>
+      <c r="O142" t="n">
+        <v>189</v>
+      </c>
+      <c r="P142" t="n">
+        <v>156</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>103</v>
+      </c>
+      <c r="R142" t="n">
+        <v>72</v>
+      </c>
+      <c r="S142" t="n">
+        <v>30</v>
+      </c>
+      <c r="T142" t="n">
         <v>9</v>
       </c>
-      <c r="O142" t="n">
-        <v>8</v>
-      </c>
-      <c r="P142" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>6</v>
-      </c>
-      <c r="R142" t="n">
-        <v>3</v>
-      </c>
-      <c r="S142" t="n">
-        <v>2</v>
-      </c>
-      <c r="T142" t="n">
-        <v>1</v>
-      </c>
       <c r="U142" t="n">
-        <v>27</v>
+        <v>494</v>
       </c>
     </row>
     <row r="143">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -11712,40 +11712,40 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>501</v>
+        <v>293</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
       </c>
       <c r="L143" t="n">
+        <v>2</v>
+      </c>
+      <c r="M143" t="n">
+        <v>2</v>
+      </c>
+      <c r="N143" t="n">
+        <v>166</v>
+      </c>
+      <c r="O143" t="n">
+        <v>145</v>
+      </c>
+      <c r="P143" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>77</v>
+      </c>
+      <c r="R143" t="n">
+        <v>58</v>
+      </c>
+      <c r="S143" t="n">
+        <v>25</v>
+      </c>
+      <c r="T143" t="n">
         <v>7</v>
       </c>
-      <c r="M143" t="n">
-        <v>7</v>
-      </c>
-      <c r="N143" t="n">
-        <v>254</v>
-      </c>
-      <c r="O143" t="n">
-        <v>189</v>
-      </c>
-      <c r="P143" t="n">
-        <v>156</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>103</v>
-      </c>
-      <c r="R143" t="n">
-        <v>72</v>
-      </c>
-      <c r="S143" t="n">
-        <v>30</v>
-      </c>
-      <c r="T143" t="n">
-        <v>9</v>
-      </c>
       <c r="U143" t="n">
-        <v>494</v>
+        <v>291</v>
       </c>
     </row>
     <row r="144">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11791,40 +11791,40 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>293</v>
+        <v>7132</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="M144" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="N144" t="n">
-        <v>166</v>
+        <v>2841</v>
       </c>
       <c r="O144" t="n">
-        <v>145</v>
+        <v>2169</v>
       </c>
       <c r="P144" t="n">
-        <v>126</v>
+        <v>1908</v>
       </c>
       <c r="Q144" t="n">
-        <v>77</v>
+        <v>1261</v>
       </c>
       <c r="R144" t="n">
-        <v>58</v>
+        <v>856</v>
       </c>
       <c r="S144" t="n">
-        <v>25</v>
+        <v>408</v>
       </c>
       <c r="T144" t="n">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="U144" t="n">
-        <v>291</v>
+        <v>7065</v>
       </c>
     </row>
     <row r="145">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -11870,40 +11870,40 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>7132</v>
+        <v>3099</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="M145" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="N145" t="n">
-        <v>2841</v>
+        <v>1099</v>
       </c>
       <c r="O145" t="n">
-        <v>2169</v>
+        <v>885</v>
       </c>
       <c r="P145" t="n">
-        <v>1908</v>
+        <v>808</v>
       </c>
       <c r="Q145" t="n">
-        <v>1261</v>
+        <v>538</v>
       </c>
       <c r="R145" t="n">
-        <v>856</v>
+        <v>365</v>
       </c>
       <c r="S145" t="n">
-        <v>408</v>
+        <v>174</v>
       </c>
       <c r="T145" t="n">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="U145" t="n">
-        <v>7065</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="146">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -11949,40 +11949,40 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>3099</v>
+        <v>2</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>1099</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
-        <v>885</v>
+        <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>538</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>3071</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -12024,11 +12024,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>2</v>
+        <v>545</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -12040,28 +12040,28 @@
         <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Q147" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="S147" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U147" t="n">
-        <v>2</v>
+        <v>545</v>
       </c>
     </row>
     <row r="148">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -12103,11 +12103,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>545</v>
+        <v>3</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -12119,28 +12119,28 @@
         <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="O148" t="n">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="P148" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="Q148" t="n">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="R148" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="S148" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>545</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -12186,7 +12186,7 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -12198,19 +12198,19 @@
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
       <c r="U149" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="150">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -12265,40 +12265,40 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>50</v>
+        <v>6715</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="O150" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="S150" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U150" t="n">
-        <v>50</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="151">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>NCL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -12344,40 +12344,40 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>6715</v>
+        <v>30</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>421</v>
+        <v>3</v>
       </c>
       <c r="M151" t="n">
-        <v>421</v>
+        <v>3</v>
       </c>
       <c r="N151" t="n">
-        <v>454</v>
+        <v>9</v>
       </c>
       <c r="O151" t="n">
-        <v>252</v>
+        <v>9</v>
       </c>
       <c r="P151" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="Q151" t="n">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="R151" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="S151" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="T151" t="n">
         <v>2</v>
       </c>
       <c r="U151" t="n">
-        <v>6392</v>
+        <v>27</v>
       </c>
     </row>
     <row r="152">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -12423,40 +12423,40 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
       </c>
       <c r="L152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -12478,12 +12478,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>NCL</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -12493,16 +12493,16 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -12581,40 +12581,40 @@
         </is>
       </c>
       <c r="J154" t="n">
+        <v>217</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
         <v>1</v>
       </c>
-      <c r="K154" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" t="n">
-        <v>0</v>
-      </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q154" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S154" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T154" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U154" t="n">
-        <v>1</v>
+        <v>217</v>
       </c>
     </row>
     <row r="155">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -12651,49 +12651,49 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>217</v>
+        <v>225137</v>
       </c>
       <c r="K155" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>7271</v>
       </c>
       <c r="M155" t="n">
-        <v>1</v>
+        <v>7444</v>
       </c>
       <c r="N155" t="n">
-        <v>35</v>
+        <v>39805</v>
       </c>
       <c r="O155" t="n">
-        <v>29</v>
+        <v>21481</v>
       </c>
       <c r="P155" t="n">
-        <v>27</v>
+        <v>16681</v>
       </c>
       <c r="Q155" t="n">
-        <v>22</v>
+        <v>8197</v>
       </c>
       <c r="R155" t="n">
-        <v>18</v>
+        <v>4558</v>
       </c>
       <c r="S155" t="n">
-        <v>12</v>
+        <v>1317</v>
       </c>
       <c r="T155" t="n">
-        <v>3</v>
+        <v>221</v>
       </c>
       <c r="U155" t="n">
-        <v>217</v>
+        <v>219116</v>
       </c>
     </row>
     <row r="156">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -12739,40 +12739,40 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>225137</v>
+        <v>4704</v>
       </c>
       <c r="K156" t="n">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="L156" t="n">
-        <v>7271</v>
+        <v>16</v>
       </c>
       <c r="M156" t="n">
-        <v>7444</v>
+        <v>133</v>
       </c>
       <c r="N156" t="n">
-        <v>39805</v>
+        <v>877</v>
       </c>
       <c r="O156" t="n">
-        <v>21481</v>
+        <v>426</v>
       </c>
       <c r="P156" t="n">
-        <v>16681</v>
+        <v>315</v>
       </c>
       <c r="Q156" t="n">
-        <v>8197</v>
+        <v>133</v>
       </c>
       <c r="R156" t="n">
-        <v>4558</v>
+        <v>84</v>
       </c>
       <c r="S156" t="n">
-        <v>1317</v>
+        <v>25</v>
       </c>
       <c r="T156" t="n">
-        <v>221</v>
+        <v>2</v>
       </c>
       <c r="U156" t="n">
-        <v>219116</v>
+        <v>4574</v>
       </c>
     </row>
     <row r="157">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -12818,40 +12818,40 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>4704</v>
+        <v>147</v>
       </c>
       <c r="K157" t="n">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="L157" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>877</v>
+        <v>14</v>
       </c>
       <c r="O157" t="n">
-        <v>426</v>
+        <v>13</v>
       </c>
       <c r="P157" t="n">
-        <v>315</v>
+        <v>13</v>
       </c>
       <c r="Q157" t="n">
-        <v>133</v>
+        <v>9</v>
       </c>
       <c r="R157" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U157" t="n">
-        <v>4574</v>
+        <v>146</v>
       </c>
     </row>
     <row r="158">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RJX</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -12897,40 +12897,40 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>147</v>
+        <v>3</v>
       </c>
       <c r="K158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P158" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>146</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159">
@@ -12942,22 +12942,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>Trenitalia France</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>national network</t>
+          <t>whole journey</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RJX</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -12976,7 +12976,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>3</v>
+        <v>273</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -12988,28 +12988,28 @@
         <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S159" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T159" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U159" t="n">
-        <v>3</v>
+        <v>273</v>
       </c>
     </row>
     <row r="160">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -13055,7 +13055,7 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>273</v>
+        <v>1</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -13067,28 +13067,28 @@
         <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -13100,32 +13100,32 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Trenitalia France</t>
+          <t>UNKNOWN_OPERATOR</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>whole journey</t>
+          <t>national network</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>BUS</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -13134,40 +13134,40 @@
         </is>
       </c>
       <c r="J161" t="n">
+        <v>3302</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>3</v>
+      </c>
+      <c r="O161" t="n">
+        <v>3</v>
+      </c>
+      <c r="P161" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>3</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2</v>
+      </c>
+      <c r="S161" t="n">
         <v>1</v>
       </c>
-      <c r="K161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="n">
-        <v>0</v>
-      </c>
-      <c r="N161" t="n">
-        <v>0</v>
-      </c>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="n">
-        <v>0</v>
-      </c>
       <c r="T161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U161" t="n">
-        <v>0</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="162">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -13213,7 +13213,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>3302</v>
+        <v>1332</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -13225,28 +13225,28 @@
         <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U162" t="n">
-        <v>3302</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="163">
@@ -13268,12 +13268,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>BUS</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -13292,7 +13292,7 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>1332</v>
+        <v>2232</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -13325,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="U163" t="n">
-        <v>1332</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="164">
@@ -13347,12 +13347,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>ECE</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -13371,7 +13371,7 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>2232</v>
+        <v>2</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
         <v>0</v>
       </c>
       <c r="U164" t="n">
-        <v>2232</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -13426,12 +13426,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>GEP</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -13450,7 +13450,7 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -13483,7 +13483,7 @@
         <v>0</v>
       </c>
       <c r="U165" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="166">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -13562,7 +13562,7 @@
         <v>0</v>
       </c>
       <c r="U166" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
     </row>
     <row r="167">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>GEP</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -13641,7 +13641,7 @@
         <v>0</v>
       </c>
       <c r="U167" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
     </row>
     <row r="168">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -13720,7 +13720,7 @@
         <v>0</v>
       </c>
       <c r="U168" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>UEX</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -13766,31 +13766,31 @@
         </is>
       </c>
       <c r="J169" t="n">
+        <v>18</v>
+      </c>
+      <c r="K169" t="n">
         <v>2</v>
       </c>
-      <c r="K169" t="n">
-        <v>0</v>
-      </c>
       <c r="L169" t="n">
         <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N169" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O169" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -13799,7 +13799,7 @@
         <v>0</v>
       </c>
       <c r="U169" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170">
@@ -13819,14 +13819,10 @@
           <t>national network</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>UEX</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -13845,40 +13841,40 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>6</v>
+      </c>
+      <c r="O170" t="n">
+        <v>4</v>
+      </c>
+      <c r="P170" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>4</v>
+      </c>
+      <c r="R170" t="n">
+        <v>3</v>
+      </c>
+      <c r="S170" t="n">
         <v>2</v>
       </c>
-      <c r="L170" t="n">
-        <v>0</v>
-      </c>
-      <c r="M170" t="n">
-        <v>2</v>
-      </c>
-      <c r="N170" t="n">
-        <v>5</v>
-      </c>
-      <c r="O170" t="n">
-        <v>5</v>
-      </c>
-      <c r="P170" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>5</v>
-      </c>
-      <c r="R170" t="n">
-        <v>5</v>
-      </c>
-      <c r="S170" t="n">
-        <v>0</v>
-      </c>
       <c r="T170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U170" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171">
@@ -13890,7 +13886,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>UZ</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -13898,10 +13894,14 @@
           <t>national network</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -13920,7 +13920,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -13932,28 +13932,28 @@
         <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P171" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U171" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
     </row>
     <row r="172">
@@ -13965,22 +13965,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>UZ</t>
+          <t>Westbahn</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>national network</t>
+          <t>whole journey</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>62</v>
+        <v>1487</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -14011,28 +14011,28 @@
         <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O172" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T172" t="n">
         <v>0</v>
       </c>
       <c r="U172" t="n">
-        <v>62</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="173">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -14078,40 +14078,40 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>1487</v>
+        <v>371</v>
       </c>
       <c r="K173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N173" t="n">
-        <v>41</v>
+        <v>203</v>
       </c>
       <c r="O173" t="n">
-        <v>36</v>
+        <v>158</v>
       </c>
       <c r="P173" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="Q173" t="n">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="R173" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="S173" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T173" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U173" t="n">
-        <v>1487</v>
+        <v>370</v>
       </c>
     </row>
     <row r="174">
@@ -14123,17 +14123,17 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Westbahn</t>
+          <t>ZSSK</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>whole journey</t>
+          <t>national network</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>371</v>
+        <v>62</v>
       </c>
       <c r="K174" t="n">
         <v>1</v>
@@ -14169,28 +14169,28 @@
         <v>1</v>
       </c>
       <c r="N174" t="n">
-        <v>203</v>
+        <v>15</v>
       </c>
       <c r="O174" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="P174" t="n">
-        <v>140</v>
+        <v>9</v>
       </c>
       <c r="Q174" t="n">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="R174" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="S174" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T174" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U174" t="n">
-        <v>370</v>
+        <v>61</v>
       </c>
     </row>
     <row r="175">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -14227,49 +14227,49 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J175" t="n">
         <v>62</v>
       </c>
       <c r="K175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O175" t="n">
+        <v>13</v>
+      </c>
+      <c r="P175" t="n">
         <v>11</v>
       </c>
-      <c r="P175" t="n">
-        <v>9</v>
-      </c>
       <c r="Q175" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R175" t="n">
         <v>5</v>
       </c>
       <c r="S175" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T175" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U175" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="176">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -14315,7 +14315,7 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
@@ -14327,28 +14327,28 @@
         <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P176" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T176" t="n">
         <v>0</v>
       </c>
       <c r="U176" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>RJX</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -14390,11 +14390,11 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -14406,106 +14406,27 @@
         <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q177" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U177" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B178" t="n">
-        <v>3</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>ZSSK</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>national network</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>RJX</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J178" t="n">
-        <v>62</v>
-      </c>
-      <c r="K178" t="n">
-        <v>0</v>
-      </c>
-      <c r="L178" t="n">
-        <v>0</v>
-      </c>
-      <c r="M178" t="n">
-        <v>0</v>
-      </c>
-      <c r="N178" t="n">
-        <v>5</v>
-      </c>
-      <c r="O178" t="n">
-        <v>5</v>
-      </c>
-      <c r="P178" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>5</v>
-      </c>
-      <c r="R178" t="n">
-        <v>5</v>
-      </c>
-      <c r="S178" t="n">
-        <v>3</v>
-      </c>
-      <c r="T178" t="n">
-        <v>2</v>
-      </c>
-      <c r="U178" t="n">
         <v>62</v>
       </c>
     </row>
@@ -14683,7 +14604,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -14695,28 +14616,28 @@
         <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q2" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R2" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="S2" t="n">
         <v>67</v>
       </c>
       <c r="T2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V2" t="n">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="3">
@@ -14767,7 +14688,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -14779,19 +14700,19 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -14800,7 +14721,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -14851,7 +14772,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -14863,16 +14784,16 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P4" t="n">
         <v>11</v>
       </c>
-      <c r="P4" t="n">
-        <v>9</v>
-      </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -14884,7 +14805,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -15031,7 +14952,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -15103,40 +15024,40 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>1009</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="P7" t="n">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="Q7" t="n">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="R7" t="n">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="S7" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="T7" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="U7" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="V7" t="n">
-        <v>1000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="8">
@@ -15187,7 +15108,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -15355,7 +15276,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -15367,17 +15288,17 @@
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -15388,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -15523,7 +15444,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2122</v>
+        <v>2141</v>
       </c>
       <c r="L12" t="n">
         <v>11</v>
@@ -15535,28 +15456,28 @@
         <v>25</v>
       </c>
       <c r="O12" t="n">
-        <v>557</v>
+        <v>590</v>
       </c>
       <c r="P12" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="Q12" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="R12" t="n">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="S12" t="n">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="T12" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="U12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="V12" t="n">
-        <v>2107</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="13">
@@ -15607,7 +15528,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -15775,7 +15696,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -15859,40 +15780,40 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>13799</v>
+        <v>14373</v>
       </c>
       <c r="L16" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M16" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="N16" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="O16" t="n">
-        <v>2856</v>
+        <v>3204</v>
       </c>
       <c r="P16" t="n">
-        <v>1575</v>
+        <v>1841</v>
       </c>
       <c r="Q16" t="n">
-        <v>1574</v>
+        <v>1840</v>
       </c>
       <c r="R16" t="n">
-        <v>1085</v>
+        <v>1249</v>
       </c>
       <c r="S16" t="n">
-        <v>853</v>
+        <v>964</v>
       </c>
       <c r="T16" t="n">
-        <v>407</v>
+        <v>474</v>
       </c>
       <c r="U16" t="n">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="V16" t="n">
-        <v>13734</v>
+        <v>14301</v>
       </c>
     </row>
     <row r="17">
@@ -15943,40 +15864,40 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>859</v>
+        <v>1172</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>307</v>
+        <v>387</v>
       </c>
       <c r="P17" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="Q17" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="R17" t="n">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="S17" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="T17" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="U17" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V17" t="n">
-        <v>859</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="18">
@@ -16027,16 +15948,16 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1033</v>
+        <v>153</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -17161,7 +17082,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L13" t="n">
         <v>15</v>
@@ -17173,13 +17094,13 @@
         <v>56</v>
       </c>
       <c r="O13" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P13" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q13" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R13" t="n">
         <v>187</v>
@@ -17194,7 +17115,7 @@
         <v>10</v>
       </c>
       <c r="V13" t="n">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14">
@@ -17329,7 +17250,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -19345,7 +19266,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L39" t="n">
         <v>4</v>
@@ -19357,13 +19278,13 @@
         <v>15</v>
       </c>
       <c r="O39" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P39" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q39" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R39" t="n">
         <v>49</v>
@@ -19378,7 +19299,7 @@
         <v>22</v>
       </c>
       <c r="V39" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40">
@@ -19429,31 +19350,31 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="L40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M40" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N40" t="n">
         <v>102</v>
       </c>
       <c r="O40" t="n">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P40" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q40" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="R40" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="S40" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="T40" t="n">
         <v>148</v>
@@ -19849,40 +19770,40 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N45" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O45" t="n">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="P45" t="n">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="Q45" t="n">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="R45" t="n">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="S45" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="T45" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="U45" t="n">
         <v>11</v>
       </c>
       <c r="V45" t="n">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="46">
@@ -19933,40 +19854,40 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O46" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="P46" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="Q46" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="R46" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="S46" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47">
@@ -20773,25 +20694,25 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
         <v>1</v>
@@ -20806,7 +20727,7 @@
         <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57">
@@ -20857,7 +20778,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -21667,16 +21588,16 @@
         <v>2915</v>
       </c>
       <c r="O8" t="n">
-        <v>4045</v>
+        <v>4049</v>
       </c>
       <c r="P8" t="n">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="Q8" t="n">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="R8" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="S8" t="n">
         <v>335</v>
@@ -21772,7 +21693,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3008</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="10">
@@ -22003,13 +21924,13 @@
         <v>3280</v>
       </c>
       <c r="O12" t="n">
-        <v>5086</v>
+        <v>5085</v>
       </c>
       <c r="P12" t="n">
         <v>2461</v>
       </c>
       <c r="Q12" t="n">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="R12" t="n">
         <v>684</v>
@@ -26700,7 +26621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27170,12 +27091,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>DB_OEBB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -27195,44 +27116,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K6" t="n">
+        <v>53</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -27254,12 +27175,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DB_OEBB</t>
+          <t>DB_OEBB_SBB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -27279,44 +27200,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>53</v>
+        <v>295</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>52</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8">
@@ -27343,7 +27264,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -27367,40 +27288,40 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>295</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -27427,7 +27348,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -27447,44 +27368,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -27506,12 +27427,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DB_OEBB_SBB</t>
+          <t>DB_SBB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -27531,44 +27452,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K10" t="n">
+        <v>124</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>33</v>
+      </c>
+      <c r="N10" t="n">
+        <v>42</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23</v>
+      </c>
+      <c r="P10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>17</v>
+      </c>
+      <c r="R10" t="n">
         <v>11</v>
       </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -27595,7 +27516,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -27619,40 +27540,40 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>124</v>
+        <v>280</v>
       </c>
       <c r="L11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>84</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12">
@@ -27679,7 +27600,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -27689,7 +27610,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -27703,40 +27624,40 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>279</v>
+        <v>1134</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="P12" t="n">
-        <v>40</v>
+        <v>151</v>
       </c>
       <c r="Q12" t="n">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="R12" t="n">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="S12" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="T12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>272</v>
+        <v>991</v>
       </c>
     </row>
     <row r="13">
@@ -27763,7 +27684,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -27773,7 +27694,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -27783,44 +27704,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1135</v>
+        <v>65</v>
       </c>
       <c r="L13" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>199</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>198</v>
+        <v>22</v>
       </c>
       <c r="P13" t="n">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="Q13" t="n">
-        <v>129</v>
+        <v>19</v>
       </c>
       <c r="R13" t="n">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="T13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="V13" t="n">
-        <v>992</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -27842,12 +27763,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DB_SBB</t>
+          <t>DB_SBB_Trenitalia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -27867,44 +27788,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="P14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="R14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -27926,12 +27847,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DB_SBB_Trenitalia</t>
+          <t>HZ_OEBB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -27951,44 +27872,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -28010,7 +27931,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HZ_OEBB</t>
+          <t>MAV_OEBB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -28051,22 +27972,22 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6</v>
+      </c>
+      <c r="S16" t="n">
         <v>5</v>
       </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -28094,12 +28015,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MAV_OEBB</t>
+          <t>OEBB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -28123,7 +28044,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -28135,28 +28056,28 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="P17" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V17" t="n">
-        <v>62</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18">
@@ -28183,7 +28104,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>RJX</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -28193,7 +28114,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -28203,44 +28124,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>130</v>
+        <v>372</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R18" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="S18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>130</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19">
@@ -28262,12 +28183,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OEBB</t>
+          <t>OEBB_SBB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RJX</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -28277,7 +28198,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -28291,40 +28212,40 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>372</v>
+        <v>279</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="P19" t="n">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="R19" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T19" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>371</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20">
@@ -28351,7 +28272,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ECE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -28366,7 +28287,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -28375,40 +28296,40 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>279</v>
+        <v>217</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="P20" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="Q20" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="R20" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="S20" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>275</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21">
@@ -28435,7 +28356,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -28450,49 +28371,49 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>217</v>
+        <v>9</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>127</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>216</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -28514,17 +28435,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OEBB_SBB</t>
+          <t>SBB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -28539,11 +28460,11 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -28555,28 +28476,28 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
         <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -28603,7 +28524,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -28627,40 +28548,40 @@
         </is>
       </c>
       <c r="K23" t="n">
+        <v>11755</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>188</v>
+      </c>
+      <c r="N23" t="n">
+        <v>213</v>
+      </c>
+      <c r="O23" t="n">
+        <v>24</v>
+      </c>
+      <c r="P23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>12</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>11579</v>
       </c>
     </row>
     <row r="24">
@@ -28692,7 +28613,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -28711,40 +28632,40 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>11755</v>
+        <v>758</v>
       </c>
       <c r="L24" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="M24" t="n">
-        <v>188</v>
+        <v>15</v>
       </c>
       <c r="N24" t="n">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="O24" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="P24" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>43</v>
+      </c>
+      <c r="R24" t="n">
+        <v>28</v>
+      </c>
+      <c r="S24" t="n">
         <v>17</v>
       </c>
-      <c r="Q24" t="n">
-        <v>12</v>
-      </c>
-      <c r="R24" t="n">
-        <v>5</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5</v>
-      </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>11579</v>
+        <v>740</v>
       </c>
     </row>
     <row r="25">
@@ -28771,17 +28692,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -28795,40 +28716,40 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>758</v>
+        <v>57</v>
       </c>
       <c r="L25" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>740</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
@@ -28855,12 +28776,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -28879,40 +28800,40 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>13225</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>13018</v>
       </c>
     </row>
     <row r="27">
@@ -28939,17 +28860,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -28963,31 +28884,31 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>57</v>
+        <v>1046</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -28996,7 +28917,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>56</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="28">
@@ -29028,7 +28949,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -29047,40 +28968,40 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>13225</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>13018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -29102,22 +29023,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>SBB_SNCF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>LYRIA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -29131,31 +29052,31 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1046</v>
+        <v>51</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -29164,7 +29085,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1017</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30">
@@ -29186,22 +29107,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>SBB_SNCF</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>LYRIA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -29215,40 +29136,40 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>844</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>837</v>
       </c>
     </row>
     <row r="31">
@@ -29280,7 +29201,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -29299,7 +29220,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -29332,7 +29253,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -29354,12 +29275,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SBB_SNCF</t>
+          <t>SBB_Trenitalia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LYRIA</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -29369,7 +29290,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -29383,40 +29304,40 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>835</v>
+        <v>1128</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
       </c>
       <c r="M32" t="n">
+        <v>27</v>
+      </c>
+      <c r="N32" t="n">
+        <v>28</v>
+      </c>
+      <c r="O32" t="n">
         <v>13</v>
       </c>
-      <c r="N32" t="n">
-        <v>14</v>
-      </c>
-      <c r="O32" t="n">
-        <v>126</v>
-      </c>
       <c r="P32" t="n">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="Q32" t="n">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="R32" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="S32" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="T32" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="U32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="V32" t="n">
-        <v>827</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="33">
@@ -29438,27 +29359,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SBB_SNCF</t>
+          <t>SBB_Trenitalia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LYRIA</t>
+          <t>ECE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -29467,31 +29388,31 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -29500,174 +29421,6 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>SBB</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>national network</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>SBB_Trenitalia</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>1128</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>27</v>
-      </c>
-      <c r="N34" t="n">
-        <v>28</v>
-      </c>
-      <c r="O34" t="n">
-        <v>13</v>
-      </c>
-      <c r="P34" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>11</v>
-      </c>
-      <c r="R34" t="n">
-        <v>8</v>
-      </c>
-      <c r="S34" t="n">
-        <v>7</v>
-      </c>
-      <c r="T34" t="n">
-        <v>6</v>
-      </c>
-      <c r="U34" t="n">
-        <v>3</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>SBB</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>national network</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>SBB_Trenitalia</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ECE</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>international</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>62</v>
-      </c>
-      <c r="L35" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6</v>
-      </c>
-      <c r="N35" t="n">
-        <v>9</v>
-      </c>
-      <c r="O35" t="n">
-        <v>10</v>
-      </c>
-      <c r="P35" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>9</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
         <v>59</v>
       </c>
     </row>
@@ -29941,25 +29694,25 @@
         <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>759</v>
@@ -30181,16 +29934,16 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>24510</v>
+        <v>24512</v>
       </c>
       <c r="L6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M6" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N6" t="n">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="O6" t="n">
         <v>4356</v>
@@ -30202,19 +29955,19 @@
         <v>2133</v>
       </c>
       <c r="R6" t="n">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="S6" t="n">
         <v>583</v>
       </c>
       <c r="T6" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
-        <v>24139</v>
+        <v>24140</v>
       </c>
     </row>
     <row r="7">
@@ -30292,7 +30045,7 @@
         <v>50</v>
       </c>
       <c r="T7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -30349,16 +30102,16 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -30781,7 +30534,7 @@
         <v>258</v>
       </c>
       <c r="O13" t="n">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="P13" t="n">
         <v>1733</v>
@@ -30853,7 +30606,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="L14" t="n">
         <v>20</v>
@@ -30865,28 +30618,28 @@
         <v>82</v>
       </c>
       <c r="O14" t="n">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="P14" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q14" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="R14" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="S14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>2921</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="15">
@@ -30937,40 +30690,40 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>162</v>
+        <v>332</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
+        <v>141</v>
+      </c>
+      <c r="P15" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>103</v>
+      </c>
+      <c r="R15" t="n">
         <v>80</v>
       </c>
-      <c r="P15" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>53</v>
-      </c>
-      <c r="R15" t="n">
-        <v>45</v>
-      </c>
       <c r="S15" t="n">
+        <v>59</v>
+      </c>
+      <c r="T15" t="n">
         <v>31</v>
       </c>
-      <c r="T15" t="n">
-        <v>17</v>
-      </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>162</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
